--- a/product_order_forms/035_factory_ventilation_grille_order_form--product_order_forms.xlsx
+++ b/product_order_forms/035_factory_ventilation_grille_order_form--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'grille_size',_'label':_'grille_size',_'type':_'select_one',_'options':_[{'id':_1,_'label':_'small'},_{'id':_2,_'label':_'large'},_{'id':_3,_'label':_'extra_large'}]}</t>
+          <t>grille_size</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'grille_size', 'label': 'Grille Size', 'type': 'select_one', 'options': [{'id': 1, 'label': 'small'}, {'id': 2, 'label': 'large'}, {'id': 3, 'label': 'extra_large'}]}</t>
+          <t>Grille Size</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'grille_pattern',_'label':_'grille_pattern',_'type':_'select_one',_'options':_[{'id':_1,_'label':_'grid'},_{'id':_2,_'label':_'mesh'},_{'id':_3,_'label':_'weave'}]}</t>
+          <t>grille_pattern</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'grille_pattern', 'label': 'Grille Pattern', 'type': 'select_one', 'options': [{'id': 1, 'label': 'grid'}, {'id': 2, 'label': 'mesh'}, {'id': 3, 'label': 'weave'}]}</t>
+          <t>Grille Pattern</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'credit_card'}</t>
+          <t>credit card</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'bank_transfer'}</t>
+          <t>bank transfer</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
     </row>
